--- a/docs/import/Suppliers.xlsx
+++ b/docs/import/Suppliers.xlsx
@@ -3376,8 +3376,10 @@
       <x:c r="AJ15" s="0" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="AK15" s="0" t="s">
-        <x:v>315</x:v>
+      <x:c r="AK15" s="0" t="inlineStr">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:37">
